--- a/01_data/01_input_data/02_processed/network_data.xlsx
+++ b/01_data/01_input_data/02_processed/network_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Nodes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Edges" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edges" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/01_data/01_input_data/02_processed/network_data.xlsx
+++ b/01_data/01_input_data/02_processed/network_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edges" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Nodes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Edges" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.80914334193531</v>
+        <v>28.82086478588354</v>
       </c>
     </row>
     <row r="8">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>61.37956396400001</v>
+        <v>61.36789729733334</v>
       </c>
     </row>
     <row r="10">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>61.36789729733334</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="11">
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.82086478588354</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="12">
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.80914334193531</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="16">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.852038590666667</v>
+        <v>61.36789729733334</v>
       </c>
     </row>
     <row r="17">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>61.36789729733334</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="19">
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18.939750164</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="20">
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27.80914334193531</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="23">
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.852038590666667</v>
+        <v>61.36789729733334</v>
       </c>
     </row>
     <row r="24">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>61.36789729733334</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="28">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3.852038590666667</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="29">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18.939750164</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="30">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="31">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="33">
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.80914334193531</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="34">
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="36">
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="38">
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="40">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="43">
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>18.939750164</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="44">
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>27.80914334193531</v>
+        <v>61.36789729733334</v>
       </c>
     </row>
     <row r="48">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>61.36789729733334</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="51">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>27.80914334193531</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="57">
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>27.80914334193531</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="58">
@@ -7900,7 +7900,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>27.39726</v>
+        <v>61.36789729733334</v>
       </c>
     </row>
     <row r="60">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>61.36789729733334</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="62">
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>27.80914334193531</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="64">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>34.70123063066669</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="65">
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>34.70123063066669</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="66">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>34.70123063066669</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="67">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>27.80914334193531</v>
+        <v>27.39726</v>
       </c>
     </row>
     <row r="69">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="74">
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="76">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="89">
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>27.80914334193531</v>
+        <v>9.154182562721894</v>
       </c>
     </row>
     <row r="90">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="91">
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9.154182562721894</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="92">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="93">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>27.80914334193531</v>
+        <v>8.95193935362129</v>
       </c>
     </row>
     <row r="95">
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8.95193935362129</v>
+        <v>15.71247390341514</v>
       </c>
     </row>
     <row r="96">
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>15.71247390341514</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="98">
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>18.939750164</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="99">
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>18.939750164</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="100">
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>27.80914334193531</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="102">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>27.80914334193531</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="103">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>27.80914334193531</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="104">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>18.939750164</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="105">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3.852038590666667</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="107">
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>18.939750164</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="108">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="109">
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>27.39726</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="110">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>18.939750164</v>
+        <v>61.36789729733334</v>
       </c>
     </row>
     <row r="111">
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>61.36789729733334</v>
+        <v>27.39726</v>
       </c>
     </row>
     <row r="112">
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>27.80914334193531</v>
+        <v>44.34948622782221</v>
       </c>
     </row>
     <row r="125">
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>27.80914334193531</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="126">
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>44.34948622782221</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="127">
@@ -8920,7 +8920,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>34.70123063066669</v>
+        <v>44.34948622782221</v>
       </c>
     </row>
     <row r="128">
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>44.34948622782221</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="129">
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>27.39726</v>
+        <v>31.0161528944889</v>
       </c>
     </row>
     <row r="139">
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>27.39726</v>
+        <v>28.62085236597335</v>
       </c>
     </row>
     <row r="140">
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>27.80914334193531</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="141">
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>27.80914334193531</v>
+        <v>27.39726</v>
       </c>
     </row>
     <row r="142">
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>27.80914334193531</v>
+        <v>90.789101532</v>
       </c>
     </row>
     <row r="143">
@@ -9175,7 +9175,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>28.62085236597335</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="145">
@@ -9190,7 +9190,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>34.70123063066669</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="146">
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>90.789101532</v>
+        <v>27.39726</v>
       </c>
     </row>
     <row r="147">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>31.0161528944889</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="148">
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>27.80914334193531</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="150">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>18.939750164</v>
+        <v>27.6507869420122</v>
       </c>
     </row>
     <row r="152">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>6.329656656031141</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="153">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="154">
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="157">
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>27.6507869420122</v>
+        <v>6.329656656031141</v>
       </c>
     </row>
     <row r="158">
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>27.80914334193531</v>
+        <v>6.329656656031141</v>
       </c>
     </row>
     <row r="163">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>6.329656656031141</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="164">
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>18.939750164</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="167">
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>9.019353756654825</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="168">
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3.852038590666667</v>
+        <v>9.019353756654825</v>
       </c>
     </row>
     <row r="169">
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>27.80914334193531</v>
+        <v>9.019353756654825</v>
       </c>
     </row>
     <row r="170">
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>9.019353756654825</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="173">
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>9.154182562721894</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="177">
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2.549933272444444</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="178">
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>27.80914334193531</v>
+        <v>9.154182562721894</v>
       </c>
     </row>
     <row r="180">
@@ -9715,7 +9715,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>27.80914334193531</v>
+        <v>2.549933272444444</v>
       </c>
     </row>
     <row r="181">
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>22.26559605067264</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="184">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>27.80914334193531</v>
+        <v>22.26559605067264</v>
       </c>
     </row>
     <row r="185">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>120.1986391</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="186">
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>48.03456396399997</v>
+        <v>31.75316844172445</v>
       </c>
     </row>
     <row r="187">
@@ -9820,7 +9820,7 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>61.37956396400001</v>
+        <v>22.26559605067264</v>
       </c>
     </row>
     <row r="188">
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>31.75316844172445</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="189">
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>22.26559605067264</v>
+        <v>48.03456396399997</v>
       </c>
     </row>
     <row r="190">
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>27.80914334193531</v>
+        <v>120.1986391</v>
       </c>
     </row>
     <row r="191">
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>54.7945</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="196">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>27.80914334193531</v>
+        <v>54.7945</v>
       </c>
     </row>
     <row r="197">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>27.80914334193531</v>
+        <v>61.36789729733329</v>
       </c>
     </row>
     <row r="208">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>90.789101532</v>
+        <v>9.828326593057239</v>
       </c>
     </row>
     <row r="210">
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>61.36789729733329</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="211">
@@ -10180,7 +10180,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>9.828326593057239</v>
+        <v>90.789101532</v>
       </c>
     </row>
     <row r="212">
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>27.80914334193531</v>
+        <v>2.549933272444444</v>
       </c>
     </row>
     <row r="213">
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2.549933272444444</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="215">
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>2.549933272444444</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="216">
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3.852038590666667</v>
+        <v>5.673398079561833</v>
       </c>
     </row>
     <row r="217">
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>3.852038590666667</v>
+        <v>2.549933272444444</v>
       </c>
     </row>
     <row r="218">
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>5.673398079561833</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="220">
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>2.549933272444444</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="225">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>27.80914334193531</v>
+        <v>2.549933272444444</v>
       </c>
     </row>
     <row r="226">
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>61.36789729733329</v>
+        <v>2.549933272444444</v>
       </c>
     </row>
     <row r="228">
@@ -10435,7 +10435,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>2.549933272444444</v>
+        <v>61.36789729733329</v>
       </c>
     </row>
     <row r="229">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>61.36789729733329</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="236">
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>27.80914334193531</v>
+        <v>61.36789729733329</v>
       </c>
     </row>
     <row r="238">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="241">
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="243">
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>56.76155012711106</v>
+        <v>15.36057079247639</v>
       </c>
     </row>
     <row r="245">
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>11.407561044</v>
+        <v>90.789101532</v>
       </c>
     </row>
     <row r="246">
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>61.36789729733329</v>
+        <v>56.76155012711106</v>
       </c>
     </row>
     <row r="247">
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>15.47177291944894</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="248">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>90.789101532</v>
+        <v>61.36789729733329</v>
       </c>
     </row>
     <row r="249">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>15.36057079247639</v>
+        <v>15.47177291944894</v>
       </c>
     </row>
     <row r="250">
@@ -10765,7 +10765,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>5.673398079561833</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="251">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>34.70123063066669</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="252">
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>11.407561044</v>
+        <v>5.673398079561833</v>
       </c>
     </row>
     <row r="253">
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>34.70123063066669</v>
+        <v>5.673398079561833</v>
       </c>
     </row>
     <row r="254">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>15.36057079247639</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="255">
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>26.3839357426327</v>
+        <v>15.36057079247639</v>
       </c>
     </row>
     <row r="256">
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>5.673398079561833</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="257">
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>27.80914334193531</v>
+        <v>26.3839357426327</v>
       </c>
     </row>
     <row r="258">
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>4.078227497778987</v>
+        <v>5.673398079561833</v>
       </c>
     </row>
     <row r="261">
@@ -10930,7 +10930,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>5.673398079561833</v>
+        <v>4.078227497778987</v>
       </c>
     </row>
     <row r="262">
@@ -10990,7 +10990,7 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>28.80510625278224</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="266">
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>61.37956396400001</v>
+        <v>28.80510625278224</v>
       </c>
     </row>
     <row r="267">
@@ -11080,7 +11080,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>120.1986391</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="272">
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>27.80914334193531</v>
+        <v>120.1986391</v>
       </c>
     </row>
     <row r="273">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>120.1986391</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="274">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>27.80914334193531</v>
+        <v>120.1986391</v>
       </c>
     </row>
     <row r="277">
@@ -11170,7 +11170,7 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="278">
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>120.1986391</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="279">
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>27.80914334193531</v>
+        <v>120.1986391</v>
       </c>
     </row>
     <row r="280">
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>115.4066252323627</v>
+        <v>8.357698884795287</v>
       </c>
     </row>
     <row r="283">
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>115.4066252323627</v>
+        <v>8.357698884795287</v>
       </c>
     </row>
     <row r="284">
@@ -11290,7 +11290,7 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>115.4066252323627</v>
+        <v>8.357698884795287</v>
       </c>
     </row>
     <row r="286">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>115.4066252323627</v>
+        <v>8.357698884795287</v>
       </c>
     </row>
     <row r="287">
@@ -11320,7 +11320,7 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>8.357698884795287</v>
+        <v>115.4066252323627</v>
       </c>
     </row>
     <row r="288">
@@ -11335,7 +11335,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>8.357698884795287</v>
+        <v>115.4066252323627</v>
       </c>
     </row>
     <row r="289">
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>8.357698884795287</v>
+        <v>115.4066252323627</v>
       </c>
     </row>
     <row r="290">
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>8.357698884795287</v>
+        <v>115.4066252323627</v>
       </c>
     </row>
     <row r="291">
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>11.407561044</v>
+        <v>45.27075566186664</v>
       </c>
     </row>
     <row r="297">
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>45.27075566186664</v>
+        <v>90.789101532</v>
       </c>
     </row>
     <row r="298">
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>90.789101532</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="299">
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>34.70123063066669</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="304">
@@ -11590,7 +11590,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>11.407561044</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="306">
@@ -11800,7 +11800,7 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>61.37956396400001</v>
+        <v>31.0161528944889</v>
       </c>
     </row>
     <row r="320">
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="321">
@@ -11830,7 +11830,7 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>31.0161528944889</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="322">
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>15.84028069306672</v>
+        <v>98.04020670753546</v>
       </c>
     </row>
     <row r="324">
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="325">
@@ -11890,7 +11890,7 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="326">
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>98.04020670753546</v>
+        <v>15.84028069306672</v>
       </c>
     </row>
     <row r="327">
@@ -11950,7 +11950,7 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>61.37956396400001</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="330">
@@ -11965,7 +11965,7 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>34.70123063066669</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="331">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="332">
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="333">
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>34.70123063066669</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="344">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>27.80914334193531</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="345">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>34.70123063066669</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="351">
@@ -12280,7 +12280,7 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="352">
@@ -12340,7 +12340,7 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>27.80914334193531</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="356">
@@ -12370,7 +12370,7 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="358">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>27.80914334193531</v>
+        <v>35.23429898274224</v>
       </c>
     </row>
     <row r="359">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>35.23429898274224</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="361">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>61.37956396400001</v>
+        <v>21.35172125620859</v>
       </c>
     </row>
     <row r="362">
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>28.80510625278224</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="363">
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>60.2739726</v>
+        <v>28.80510625278224</v>
       </c>
     </row>
     <row r="364">
@@ -12475,7 +12475,7 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>21.35172125620859</v>
+        <v>60.2739726</v>
       </c>
     </row>
     <row r="365">
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>61.37956396400001</v>
+        <v>28.80510625278224</v>
       </c>
     </row>
     <row r="366">
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>28.80510625278224</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="367">
@@ -12520,7 +12520,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>61.37956396400001</v>
+        <v>28.80510625278224</v>
       </c>
     </row>
     <row r="368">
@@ -12535,7 +12535,7 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>28.80510625278224</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="369">
@@ -12550,7 +12550,7 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>61.37956396400001</v>
+        <v>28.80510625278224</v>
       </c>
     </row>
     <row r="370">
@@ -12565,7 +12565,7 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>28.80510625278224</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="371">
@@ -12580,7 +12580,7 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="372">
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>61.37956396400001</v>
+        <v>60.2739726</v>
       </c>
     </row>
     <row r="375">
@@ -12640,7 +12640,7 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>60.2739726</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="376">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>90.789101532</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="377">
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>27.80914334193531</v>
+        <v>90.789101532</v>
       </c>
     </row>
     <row r="378">
@@ -12745,7 +12745,7 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>76.08433274799999</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="383">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>27.80914334193531</v>
+        <v>76.08433274799999</v>
       </c>
     </row>
     <row r="384">
@@ -12775,7 +12775,7 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>76.08433274799999</v>
+        <v>90.789101532</v>
       </c>
     </row>
     <row r="385">
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>90.789101532</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="386">
@@ -12820,7 +12820,7 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>61.37956396400001</v>
+        <v>76.08433274799999</v>
       </c>
     </row>
     <row r="388">
@@ -12835,7 +12835,7 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>76.08433274799999</v>
+        <v>9.019353756654825</v>
       </c>
     </row>
     <row r="389">
@@ -12865,7 +12865,7 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>9.019353756654825</v>
+        <v>76.08433274799999</v>
       </c>
     </row>
     <row r="391">
@@ -12910,7 +12910,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>76.08433274799999</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="394">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>61.37956396400001</v>
+        <v>76.08433274799999</v>
       </c>
     </row>
     <row r="395">
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>76.08433274799999</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="397">
@@ -13000,7 +13000,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>27.80914334193531</v>
+        <v>76.08433274799999</v>
       </c>
     </row>
     <row r="400">
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="402">
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>61.37956396400001</v>
+        <v>76.08433274799999</v>
       </c>
     </row>
     <row r="405">
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>76.08433274799999</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="406">
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>48.80510625278217</v>
+        <v>19.98809670132093</v>
       </c>
     </row>
     <row r="407">
@@ -13120,7 +13120,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>61.37956396400001</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="408">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>19.98809670132093</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="409">
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>48.80510625278217</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="410">
@@ -13165,7 +13165,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>61.37956396400001</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="411">
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>48.80510625278217</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="412">
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>61.37956396400001</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="413">
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>48.80510625278217</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="414">
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>61.37956396400001</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="415">
@@ -13240,7 +13240,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>48.80510625278217</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="416">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>61.37956396400001</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="417">
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>48.80510625278217</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="418">
@@ -13285,7 +13285,7 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>61.37956396400001</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="419">
@@ -13360,7 +13360,7 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>48.80510625278217</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="424">
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>61.37956396400001</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="425">
@@ -13390,7 +13390,7 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>48.80510625278217</v>
+        <v>44.34948622782221</v>
       </c>
     </row>
     <row r="426">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>61.37956396400001</v>
+        <v>44.34948622782221</v>
       </c>
     </row>
     <row r="428">
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>76.08433274799999</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="429">
@@ -13450,7 +13450,7 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>44.34948622782221</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="430">
@@ -13465,7 +13465,7 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>44.34948622782221</v>
+        <v>3.37826986501199</v>
       </c>
     </row>
     <row r="431">
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>3.37826986501199</v>
+        <v>76.08433274799999</v>
       </c>
     </row>
     <row r="433">
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>48.80510625278217</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="436">
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="437">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>27.80914334193531</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="438">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>48.80510625278217</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="439">
@@ -13600,7 +13600,7 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>61.37956396400001</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="440">
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>8.614867338453617</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="444">
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>18.939750164</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="445">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>48.80510625278217</v>
+        <v>8.614867338453617</v>
       </c>
     </row>
     <row r="446">
@@ -13720,7 +13720,7 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>48.80510625278217</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="448">
@@ -13780,7 +13780,7 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>2</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="452">
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>48.80510625278217</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="453">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>61.37956396400001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -13825,7 +13825,7 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>27.80914334193531</v>
+        <v>48.80510625278217</v>
       </c>
     </row>
     <row r="455">
@@ -13870,7 +13870,7 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>61.37956396400001</v>
+        <v>76.08433274799999</v>
       </c>
     </row>
     <row r="458">
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>76.08433274799999</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="459">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="470">
@@ -14065,7 +14065,7 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="471">
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>27.80914334193531</v>
+        <v>65.7534</v>
       </c>
     </row>
     <row r="475">
@@ -14140,7 +14140,7 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="476">
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>65.7534</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="477">
@@ -14170,7 +14170,7 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>90.789101532</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="478">
@@ -14200,7 +14200,7 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="480">
@@ -14215,7 +14215,7 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>61.37956396400001</v>
+        <v>90.789101532</v>
       </c>
     </row>
     <row r="481">
@@ -14230,7 +14230,7 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="482">
@@ -14275,7 +14275,7 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>39.74313905759999</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="485">
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>31.93742232853334</v>
+        <v>39.74313905759999</v>
       </c>
     </row>
     <row r="488">
@@ -14335,7 +14335,7 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>31.93742232853334</v>
+        <v>20.88218912000002</v>
       </c>
     </row>
     <row r="489">
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>20.88218912000002</v>
+        <v>31.93742232853334</v>
       </c>
     </row>
     <row r="490">
@@ -14365,7 +14365,7 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>27.80914334193531</v>
+        <v>31.93742232853334</v>
       </c>
     </row>
     <row r="491">
@@ -14440,7 +14440,7 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>27.80914334193531</v>
+        <v>33.97624536113621</v>
       </c>
     </row>
     <row r="496">
@@ -14500,7 +14500,7 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>33.97624536113621</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="500">
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>27.80914334193531</v>
+        <v>28.2619408592569</v>
       </c>
     </row>
     <row r="501">
@@ -14530,7 +14530,7 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>28.2619408592569</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="502">
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>27.80914334193531</v>
+        <v>9.154182562721894</v>
       </c>
     </row>
     <row r="504">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>27.80914334193531</v>
+        <v>15.84028069306672</v>
       </c>
     </row>
     <row r="505">
@@ -14605,7 +14605,7 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>15.84028069306672</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="507">
@@ -14620,7 +14620,7 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>9.154182562721894</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="508">
@@ -14875,7 +14875,7 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="525">
@@ -14890,7 +14890,7 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="526">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>3.852038590666667</v>
+        <v>9.154182562721894</v>
       </c>
     </row>
     <row r="527">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>9.154182562721894</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="528">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>9.154182562721894</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="531">
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>3.852038590666667</v>
+        <v>9.154182562721894</v>
       </c>
     </row>
     <row r="533">
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>61.37956396400001</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="535">
@@ -15040,7 +15040,7 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>3.852038590666667</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="536">
@@ -15055,7 +15055,7 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>90.789101532</v>
+        <v>15.84028069306672</v>
       </c>
     </row>
     <row r="537">
@@ -15070,7 +15070,7 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>27.80914334193531</v>
+        <v>90.789101532</v>
       </c>
     </row>
     <row r="538">
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>15.84028069306672</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="540">
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>90.789101532</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="543">
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>27.80914334193531</v>
+        <v>90.789101532</v>
       </c>
     </row>
     <row r="544">
@@ -15205,7 +15205,7 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="547">
@@ -15250,7 +15250,7 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="550">
@@ -15265,7 +15265,7 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>50.66219357336974</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="551">
@@ -15280,7 +15280,7 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>27.80914334193531</v>
+        <v>50.66219357336974</v>
       </c>
     </row>
     <row r="552">
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="553">
@@ -15310,7 +15310,7 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="554">
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="C556" t="n">
-        <v>15.84028069306672</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="557">
@@ -15370,7 +15370,7 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>27.80914334193531</v>
+        <v>8.95193935362129</v>
       </c>
     </row>
     <row r="558">
@@ -15385,7 +15385,7 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>8.95193935362129</v>
+        <v>15.84028069306672</v>
       </c>
     </row>
     <row r="559">
@@ -15415,7 +15415,7 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="561">
@@ -15430,7 +15430,7 @@
         </is>
       </c>
       <c r="C561" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="562">
@@ -15520,7 +15520,7 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>27.80914334193531</v>
+        <v>6.334255996897481</v>
       </c>
     </row>
     <row r="568">
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>6.334255996897481</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="569">
@@ -15775,7 +15775,7 @@
         </is>
       </c>
       <c r="C584" t="n">
-        <v>9.154182562721894</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="585">
@@ -15805,7 +15805,7 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>27.80914334193531</v>
+        <v>9.154182562721894</v>
       </c>
     </row>
     <row r="587">
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>44.34948622782221</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="593">
@@ -15910,7 +15910,7 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>27.80914334193531</v>
+        <v>44.34948622782221</v>
       </c>
     </row>
     <row r="594">
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="C602" t="n">
-        <v>6.329656656031141</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="603">
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>27.80914334193531</v>
+        <v>6.329656656031141</v>
       </c>
     </row>
     <row r="604">
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="C609" t="n">
-        <v>27.80914334193531</v>
+        <v>6.329656656031141</v>
       </c>
     </row>
     <row r="610">
@@ -16165,7 +16165,7 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>6.329656656031141</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="611">
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="613">
@@ -16210,7 +16210,7 @@
         </is>
       </c>
       <c r="C613" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="614">
@@ -16285,7 +16285,7 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>3.852038590666667</v>
+        <v>6.329656656031141</v>
       </c>
     </row>
     <row r="619">
@@ -16300,7 +16300,7 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>6.329656656031141</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="620">
@@ -16360,7 +16360,7 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>3.852038590666667</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="624">
@@ -16375,7 +16375,7 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>27.80914334193531</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="625">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>34.70123063066669</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="637">
@@ -16570,7 +16570,7 @@
         </is>
       </c>
       <c r="C637" t="n">
-        <v>27.80914334193531</v>
+        <v>34.70123063066669</v>
       </c>
     </row>
     <row r="638">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="651">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="C652" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="653">
@@ -17020,7 +17020,7 @@
         </is>
       </c>
       <c r="C667" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="668">
@@ -17035,7 +17035,7 @@
         </is>
       </c>
       <c r="C668" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="669">
@@ -17155,7 +17155,7 @@
         </is>
       </c>
       <c r="C676" t="n">
-        <v>11.407561044</v>
+        <v>3.875371924000021</v>
       </c>
     </row>
     <row r="677">
@@ -17170,7 +17170,7 @@
         </is>
       </c>
       <c r="C677" t="n">
-        <v>3.875371924000021</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="678">
@@ -17185,7 +17185,7 @@
         </is>
       </c>
       <c r="C678" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="679">
@@ -17200,7 +17200,7 @@
         </is>
       </c>
       <c r="C679" t="n">
-        <v>11.407561044</v>
+        <v>45.27075566186664</v>
       </c>
     </row>
     <row r="680">
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="C682" t="n">
-        <v>45.27075566186664</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="683">
@@ -17260,7 +17260,7 @@
         </is>
       </c>
       <c r="C683" t="n">
-        <v>3.875371924000021</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="684">
@@ -17290,7 +17290,7 @@
         </is>
       </c>
       <c r="C685" t="n">
-        <v>11.407561044</v>
+        <v>3.875371924000021</v>
       </c>
     </row>
     <row r="686">
@@ -17455,7 +17455,7 @@
         </is>
       </c>
       <c r="C696" t="n">
-        <v>31.75316844172445</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="697">
@@ -17485,7 +17485,7 @@
         </is>
       </c>
       <c r="C698" t="n">
-        <v>27.80914334193531</v>
+        <v>31.75316844172445</v>
       </c>
     </row>
     <row r="699">
@@ -17590,7 +17590,7 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>3.875371924000021</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="706">
@@ -17605,7 +17605,7 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>11.407561044</v>
+        <v>120.1986391</v>
       </c>
     </row>
     <row r="707">
@@ -17650,7 +17650,7 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>120.1986391</v>
+        <v>3.875371924000021</v>
       </c>
     </row>
     <row r="710">
@@ -17755,7 +17755,7 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="717">
@@ -17770,7 +17770,7 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="718">
@@ -17905,7 +17905,7 @@
         </is>
       </c>
       <c r="C726" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="727">
@@ -17920,7 +17920,7 @@
         </is>
       </c>
       <c r="C727" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="728">
@@ -17935,7 +17935,7 @@
         </is>
       </c>
       <c r="C728" t="n">
-        <v>27.80914334193531</v>
+        <v>3.875371924000021</v>
       </c>
     </row>
     <row r="729">
@@ -17950,7 +17950,7 @@
         </is>
       </c>
       <c r="C729" t="n">
-        <v>3.875371924000021</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="730">
@@ -17965,7 +17965,7 @@
         </is>
       </c>
       <c r="C730" t="n">
-        <v>45.27075566186664</v>
+        <v>15.926874516</v>
       </c>
     </row>
     <row r="731">
@@ -17980,7 +17980,7 @@
         </is>
       </c>
       <c r="C731" t="n">
-        <v>3.875371924000021</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="732">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="C732" t="n">
-        <v>15.926874516</v>
+        <v>3.875371924000021</v>
       </c>
     </row>
     <row r="733">
@@ -18010,7 +18010,7 @@
         </is>
       </c>
       <c r="C733" t="n">
-        <v>3.875371924000021</v>
+        <v>45.27075566186664</v>
       </c>
     </row>
     <row r="734">
@@ -18025,7 +18025,7 @@
         </is>
       </c>
       <c r="C734" t="n">
-        <v>27.80914334193531</v>
+        <v>3.875371924000021</v>
       </c>
     </row>
     <row r="735">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="C735" t="n">
-        <v>36.43456396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="736">
@@ -18055,7 +18055,7 @@
         </is>
       </c>
       <c r="C736" t="n">
-        <v>27.80914334193531</v>
+        <v>36.43456396400001</v>
       </c>
     </row>
     <row r="737">
@@ -18100,7 +18100,7 @@
         </is>
       </c>
       <c r="C739" t="n">
-        <v>120.1986391</v>
+        <v>45.27075566186664</v>
       </c>
     </row>
     <row r="740">
@@ -18115,7 +18115,7 @@
         </is>
       </c>
       <c r="C740" t="n">
-        <v>15.926874516</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="741">
@@ -18130,7 +18130,7 @@
         </is>
       </c>
       <c r="C741" t="n">
-        <v>11.407561044</v>
+        <v>120.1986391</v>
       </c>
     </row>
     <row r="742">
@@ -18175,7 +18175,7 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>11.407561044</v>
+        <v>15.926874516</v>
       </c>
     </row>
     <row r="745">
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>45.27075566186664</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="746">
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="C751" t="n">
-        <v>15.926874516</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="752">
@@ -18340,7 +18340,7 @@
         </is>
       </c>
       <c r="C755" t="n">
-        <v>11.407561044</v>
+        <v>36.43456396400001</v>
       </c>
     </row>
     <row r="756">
@@ -18355,7 +18355,7 @@
         </is>
       </c>
       <c r="C756" t="n">
-        <v>36.43456396400001</v>
+        <v>15.926874516</v>
       </c>
     </row>
     <row r="757">
@@ -18430,7 +18430,7 @@
         </is>
       </c>
       <c r="C761" t="n">
-        <v>5.227637537054379</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="762">
@@ -18445,7 +18445,7 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>11.407561044</v>
+        <v>36.43456396400001</v>
       </c>
     </row>
     <row r="763">
@@ -18460,7 +18460,7 @@
         </is>
       </c>
       <c r="C763" t="n">
-        <v>36.43456396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="764">
@@ -18490,7 +18490,7 @@
         </is>
       </c>
       <c r="C765" t="n">
-        <v>27.80914334193531</v>
+        <v>5.227637537054379</v>
       </c>
     </row>
     <row r="766">
@@ -18685,7 +18685,7 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="779">
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="C779" t="n">
-        <v>3.875371924000021</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="780">
@@ -18715,7 +18715,7 @@
         </is>
       </c>
       <c r="C780" t="n">
-        <v>11.407561044</v>
+        <v>3.875371924000021</v>
       </c>
     </row>
     <row r="781">
@@ -18730,7 +18730,7 @@
         </is>
       </c>
       <c r="C781" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="782">
@@ -18760,7 +18760,7 @@
         </is>
       </c>
       <c r="C783" t="n">
-        <v>11.407561044</v>
+        <v>39.74313905759999</v>
       </c>
     </row>
     <row r="784">
@@ -18775,7 +18775,7 @@
         </is>
       </c>
       <c r="C784" t="n">
-        <v>39.74313905759999</v>
+        <v>15.926874516</v>
       </c>
     </row>
     <row r="785">
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="C786" t="n">
-        <v>15.926874516</v>
+        <v>39.74313905759999</v>
       </c>
     </row>
     <row r="787">
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="C787" t="n">
-        <v>39.74313905759999</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="788">
@@ -18835,7 +18835,7 @@
         </is>
       </c>
       <c r="C788" t="n">
-        <v>39.74313905759999</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="789">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="C790" t="n">
-        <v>27.80914334193531</v>
+        <v>39.74313905759999</v>
       </c>
     </row>
     <row r="791">
@@ -18880,7 +18880,7 @@
         </is>
       </c>
       <c r="C791" t="n">
-        <v>39.74313905759999</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="792">
@@ -18895,7 +18895,7 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>39.74313905759999</v>
+        <v>120.1986391</v>
       </c>
     </row>
     <row r="793">
@@ -18925,7 +18925,7 @@
         </is>
       </c>
       <c r="C794" t="n">
-        <v>120.1986391</v>
+        <v>39.74313905759999</v>
       </c>
     </row>
     <row r="795">
@@ -18940,7 +18940,7 @@
         </is>
       </c>
       <c r="C795" t="n">
-        <v>11.407561044</v>
+        <v>39.74313905759999</v>
       </c>
     </row>
     <row r="796">
@@ -18955,7 +18955,7 @@
         </is>
       </c>
       <c r="C796" t="n">
-        <v>20.88218912000002</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="797">
@@ -18970,7 +18970,7 @@
         </is>
       </c>
       <c r="C797" t="n">
-        <v>31.93742232853334</v>
+        <v>20.88218912000002</v>
       </c>
     </row>
     <row r="798">
@@ -18985,7 +18985,7 @@
         </is>
       </c>
       <c r="C798" t="n">
-        <v>27.80914334193531</v>
+        <v>31.93742232853334</v>
       </c>
     </row>
     <row r="799">
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>27.80914334193531</v>
+        <v>20.88218912000002</v>
       </c>
     </row>
     <row r="804">
@@ -19075,7 +19075,7 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>20.88218912000002</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="805">
@@ -19180,7 +19180,7 @@
         </is>
       </c>
       <c r="C811" t="n">
-        <v>20.88218912000002</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="812">
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="C812" t="n">
-        <v>27.80914334193531</v>
+        <v>20.88218912000002</v>
       </c>
     </row>
     <row r="813">
@@ -19255,7 +19255,7 @@
         </is>
       </c>
       <c r="C816" t="n">
-        <v>20.88218912000002</v>
+        <v>31.93742232853334</v>
       </c>
     </row>
     <row r="817">
@@ -19285,7 +19285,7 @@
         </is>
       </c>
       <c r="C818" t="n">
-        <v>31.93742232853334</v>
+        <v>20.88218912000002</v>
       </c>
     </row>
     <row r="819">
@@ -19390,7 +19390,7 @@
         </is>
       </c>
       <c r="C825" t="n">
-        <v>31.93742232853334</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="826">
@@ -19405,7 +19405,7 @@
         </is>
       </c>
       <c r="C826" t="n">
-        <v>11.407561044</v>
+        <v>31.93742232853334</v>
       </c>
     </row>
     <row r="827">
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="C827" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="828">
@@ -19435,7 +19435,7 @@
         </is>
       </c>
       <c r="C828" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="829">
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="C829" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="830">
@@ -19465,7 +19465,7 @@
         </is>
       </c>
       <c r="C830" t="n">
-        <v>2.549933272444444</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="831">
@@ -19480,7 +19480,7 @@
         </is>
       </c>
       <c r="C831" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="832">
@@ -19495,7 +19495,7 @@
         </is>
       </c>
       <c r="C832" t="n">
-        <v>27.80914334193531</v>
+        <v>2.549933272444444</v>
       </c>
     </row>
     <row r="833">
@@ -19555,7 +19555,7 @@
         </is>
       </c>
       <c r="C836" t="n">
-        <v>2.549933272444444</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="837">
@@ -19585,7 +19585,7 @@
         </is>
       </c>
       <c r="C838" t="n">
-        <v>27.80914334193531</v>
+        <v>2.549933272444444</v>
       </c>
     </row>
     <row r="839">
@@ -19825,7 +19825,7 @@
         </is>
       </c>
       <c r="C854" t="n">
-        <v>5.673398079561833</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="855">
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="C855" t="n">
-        <v>27.80914334193531</v>
+        <v>5.673398079561833</v>
       </c>
     </row>
     <row r="856">
@@ -19855,7 +19855,7 @@
         </is>
       </c>
       <c r="C856" t="n">
-        <v>2.549933272444444</v>
+        <v>5.673398079561833</v>
       </c>
     </row>
     <row r="857">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="C857" t="n">
-        <v>5.673398079561833</v>
+        <v>2.549933272444444</v>
       </c>
     </row>
     <row r="858">
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="C862" t="n">
-        <v>27.80914334193531</v>
+        <v>2</v>
       </c>
     </row>
     <row r="863">
@@ -19960,7 +19960,7 @@
         </is>
       </c>
       <c r="C863" t="n">
-        <v>2</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="864">
@@ -20020,7 +20020,7 @@
         </is>
       </c>
       <c r="C867" t="n">
-        <v>45.27075566186664</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="868">
@@ -20035,7 +20035,7 @@
         </is>
       </c>
       <c r="C868" t="n">
-        <v>27.80914334193531</v>
+        <v>45.27075566186664</v>
       </c>
     </row>
     <row r="869">
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="C872" t="n">
-        <v>4.976897231893936</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="873">
@@ -20110,7 +20110,7 @@
         </is>
       </c>
       <c r="C873" t="n">
-        <v>11.407561044</v>
+        <v>4.976897231893936</v>
       </c>
     </row>
     <row r="874">
@@ -20230,7 +20230,7 @@
         </is>
       </c>
       <c r="C881" t="n">
-        <v>27.80914334193531</v>
+        <v>5.930523686411172</v>
       </c>
     </row>
     <row r="882">
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="C882" t="n">
-        <v>5.930523686411172</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="883">
@@ -20260,7 +20260,7 @@
         </is>
       </c>
       <c r="C883" t="n">
-        <v>3.875371924000021</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="884">
@@ -20275,7 +20275,7 @@
         </is>
       </c>
       <c r="C884" t="n">
-        <v>11.407561044</v>
+        <v>3.875371924000021</v>
       </c>
     </row>
     <row r="885">
@@ -20290,7 +20290,7 @@
         </is>
       </c>
       <c r="C885" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="886">
@@ -20350,7 +20350,7 @@
         </is>
       </c>
       <c r="C889" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="890">
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="C892" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="893">
@@ -20425,7 +20425,7 @@
         </is>
       </c>
       <c r="C894" t="n">
-        <v>27.80914334193531</v>
+        <v>11.407561044</v>
       </c>
     </row>
     <row r="895">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="C895" t="n">
-        <v>11.407561044</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="896">
@@ -20635,7 +20635,7 @@
         </is>
       </c>
       <c r="C908" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="909">
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="C909" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="910">
@@ -20680,7 +20680,7 @@
         </is>
       </c>
       <c r="C911" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="912">
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="C912" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="913">
@@ -20725,7 +20725,7 @@
         </is>
       </c>
       <c r="C914" t="n">
-        <v>61.37956396400001</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="915">
@@ -20755,7 +20755,7 @@
         </is>
       </c>
       <c r="C916" t="n">
-        <v>27.80914334193531</v>
+        <v>61.37956396400001</v>
       </c>
     </row>
     <row r="917">
@@ -20800,7 +20800,7 @@
         </is>
       </c>
       <c r="C919" t="n">
-        <v>3.852038590666667</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="920">
@@ -20815,7 +20815,7 @@
         </is>
       </c>
       <c r="C920" t="n">
-        <v>18.939750164</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="921">
@@ -20830,7 +20830,7 @@
         </is>
       </c>
       <c r="C921" t="n">
-        <v>18.939750164</v>
+        <v>2.234584754461056</v>
       </c>
     </row>
     <row r="922">
@@ -20845,7 +20845,7 @@
         </is>
       </c>
       <c r="C922" t="n">
-        <v>3.852038590666667</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="923">
@@ -20860,7 +20860,7 @@
         </is>
       </c>
       <c r="C923" t="n">
-        <v>2.234584754461056</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="924">
@@ -20905,7 +20905,7 @@
         </is>
       </c>
       <c r="C926" t="n">
-        <v>8.345209726319478</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="927">
@@ -20920,7 +20920,7 @@
         </is>
       </c>
       <c r="C927" t="n">
-        <v>8.95193935362129</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="928">
@@ -20935,7 +20935,7 @@
         </is>
       </c>
       <c r="C928" t="n">
-        <v>27.80914334193531</v>
+        <v>8.345209726319478</v>
       </c>
     </row>
     <row r="929">
@@ -20950,7 +20950,7 @@
         </is>
       </c>
       <c r="C929" t="n">
-        <v>3.852038590666667</v>
+        <v>8.95193935362129</v>
       </c>
     </row>
     <row r="930">
@@ -21055,7 +21055,7 @@
         </is>
       </c>
       <c r="C936" t="n">
-        <v>3.852038590666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="937">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="C937" t="n">
-        <v>2</v>
+        <v>3.852038590666667</v>
       </c>
     </row>
     <row r="938">
@@ -21205,7 +21205,7 @@
         </is>
       </c>
       <c r="C946" t="n">
-        <v>8.412624129353013</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="947">
@@ -21250,7 +21250,7 @@
         </is>
       </c>
       <c r="C949" t="n">
-        <v>18.939750164</v>
+        <v>8.412624129353013</v>
       </c>
     </row>
     <row r="950">
@@ -21325,7 +21325,7 @@
         </is>
       </c>
       <c r="C954" t="n">
-        <v>8.614867338453617</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="955">
@@ -21340,7 +21340,7 @@
         </is>
       </c>
       <c r="C955" t="n">
-        <v>18.939750164</v>
+        <v>8.614867338453617</v>
       </c>
     </row>
     <row r="956">
@@ -21415,7 +21415,7 @@
         </is>
       </c>
       <c r="C960" t="n">
-        <v>18.939750164</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="961">
@@ -21430,7 +21430,7 @@
         </is>
       </c>
       <c r="C961" t="n">
-        <v>27.80914334193531</v>
+        <v>18.939750164</v>
       </c>
     </row>
     <row r="962">
@@ -21460,7 +21460,7 @@
         </is>
       </c>
       <c r="C963" t="n">
-        <v>53.26072627774218</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="964">
@@ -21490,7 +21490,7 @@
         </is>
       </c>
       <c r="C965" t="n">
-        <v>27.80914334193531</v>
+        <v>53.26072627774218</v>
       </c>
     </row>
     <row r="966">
@@ -21535,7 +21535,7 @@
         </is>
       </c>
       <c r="C968" t="n">
-        <v>53.26072627774218</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="969">
@@ -21550,7 +21550,7 @@
         </is>
       </c>
       <c r="C969" t="n">
-        <v>27.80914334193531</v>
+        <v>53.26072627774218</v>
       </c>
     </row>
     <row r="970">
@@ -21880,7 +21880,7 @@
         </is>
       </c>
       <c r="C991" t="n">
-        <v>21.35172125620859</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="992">
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="C992" t="n">
-        <v>27.80914334193531</v>
+        <v>21.35172125620859</v>
       </c>
     </row>
     <row r="993">
@@ -21925,7 +21925,7 @@
         </is>
       </c>
       <c r="C994" t="n">
-        <v>29.27347589119965</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="995">
@@ -21940,7 +21940,7 @@
         </is>
       </c>
       <c r="C995" t="n">
-        <v>27.80914334193531</v>
+        <v>29.27347589119965</v>
       </c>
     </row>
     <row r="996">
@@ -22315,7 +22315,7 @@
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>27.80914334193531</v>
+        <v>65.7534</v>
       </c>
     </row>
     <row r="1021">
@@ -22330,7 +22330,7 @@
         </is>
       </c>
       <c r="C1021" t="n">
-        <v>65.7534</v>
+        <v>27.80914334193531</v>
       </c>
     </row>
     <row r="1022">
